--- a/travel_feedback_forms/011_travel_package_experience_assessment--travel_feedback_forms.xlsx
+++ b/travel_feedback_forms/011_travel_package_experience_assessment--travel_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_5}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 5}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_4}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Very good', 'value': 4}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_2}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 2}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'terrible',_'value':_1}</t>
+          <t>terrible</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Terrible', 'value': 1}</t>
+          <t>Terrible</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'domestic',_'value':_'domestic'}</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Domestic', 'value': 'Domestic'}</t>
+          <t>Domestic</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'international',_'value':_'international'}</t>
+          <t>international</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'International', 'value': 'International'}</t>
+          <t>International</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'hotel',_'value':_'hotel'}</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Hotel', 'value': 'Hotel'}</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'hostel',_'value':_'hostel'}</t>
+          <t>hostel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Hostel', 'value': 'Hostel'}</t>
+          <t>Hostel</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
